--- a/Fandom_matching table.xlsx
+++ b/Fandom_matching table.xlsx
@@ -13,7 +13,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$2:$H$226</definedName>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="722">
   <si>
     <t>aid</t>
   </si>
@@ -2101,53 +2100,6 @@
   </si>
   <si>
     <t>수집기간</t>
-  </si>
-  <si>
-    <t>GD X TAEYANG</t>
-  </si>
-  <si>
-    <t>레드벨벳(Red Velvet)</t>
-  </si>
-  <si>
-    <r>
-      <t>빅스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>LR</t>
-    </r>
-  </si>
-  <si>
-    <t>저스투 (Jus2)</t>
-  </si>
-  <si>
-    <t>소현</t>
-  </si>
-  <si>
-    <t>민석</t>
-  </si>
-  <si>
-    <t>아아린</t>
-  </si>
-  <si>
-    <t>재훈</t>
-  </si>
-  <si>
-    <t>비진</t>
-  </si>
-  <si>
-    <t>윤서</t>
-  </si>
-  <si>
-    <t>병한</t>
-  </si>
-  <si>
-    <t>아티스트명 담당자 수집 시작일 수집 종료일 예상 수집 기간 (여자)아이들 ((G)I-DLE) 소현 2025-05-04 2025-05-06 2025-05-04 ~ 2025-05-06 2NE1 민석 2025-05-04 2025-05-04 2025-05-04 B.A.P 소현 2025-05-06 2025-05-06 2025-05-06 JBJ 민석 2025-05-04 2025-05-04 2025-05-04 WayV 소현 2025-05-06 2025-05-06 2025-05-06 갓세븐 (GOT7) 민석 2025-05-04 2025-05-04 2025-05-04 골든차일드 소현 2025-05-06 2025-05-06 2025-05-06 나연 민석 2025-05-04 2025-05-04 2025-05-04 뉴진스 (NewJeans) 소현 2025-05-06 2025-05-08 2025-05-06 ~ 2025-05-08 더보이즈(THE BOYZ) 민석 2025-05-04 2025-05-05 2025-05-04 ~ 2025-05-05 데이식스(DAY6) 소현 2025-05-08 2025-05-10 2025-05-08 ~ 2025-05-10 드림캐쳐 민석 2025-05-05 2025-05-05 2025-05-05 라이즈 (RIIZE) 소현 2025-05-10 2025-05-12 2025-05-10 ~ 2025-05-12 러블리즈 민석 2025-05-05 2025-05-05 2025-05-05 로제 (ROSE) 소현 2025-05-12 2025-05-13 2025-05-12 ~ 2025-05-13 르세라핌 (LE SSERAFIM) 민석 2025-05-05 2025-05-07 2025-05-05 ~ 2025-05-07 리사 (LISA) 소현 2025-05-13 2025-05-13 2025-05-13 마마무 (Mamamoo) 민석 2025-05-07 2025-05-07 2025-05-07 몬스타엑스 소현 2025-05-13 2025-05-14 2025-05-13 ~ 2025-05-14 방탄소년단 민석 2025-05-07 2025-05-09 2025-05-07 ~ 2025-05-09 보이넥스트도어 (BOYNEXTDOOR) 소현 2025-05-14 2025-05-15 2025-05-14 ~ 2025-05-15 블락비 (Block B) 민석 2025-05-09 2025-05-09 2025-05-09 비원에이포 (B1A4) 소현 2025-05-15 2025-05-15 2025-05-15 비투비 (BTOB) 민석 2025-05-09 2025-05-09 2025-05-09 빅뱅 (BIGBANG) 소현 2025-05-15 2025-05-16 2025-05-15 ~ 2025-05-16 빅톤 (VICTON) 민석 2025-05-09 2025-05-09 2025-05-09 샤이니 (SHINee) 소현 2025-05-16 2025-05-17 2025-05-16 ~ 2025-05-17 세븐틴 (SEVENTEEN) 민석 2025-05-09 2025-05-11 2025-05-09 ~ 2025-05-11 솔라 (마마무) 소현 2025-05-17 2025-05-17 2025-05-17 슈퍼엠 (SuperM) 민석 2025-05-11 2025-05-11 2025-05-11 슈퍼주니어 (Super Junior) 소현 2025-05-17 2025-05-17 2025-05-17 스테이씨 (STAYC) 민석 2025-05-11 2025-05-12 2025-05-11 ~ 2025-05-12 슬기 (SEULGI) 소현 2025-05-17 2025-05-17 2025-05-17 씨아이엑스 (CIX) 민석 2025-05-12 2025-05-12 2025-05-12 씨엔블루 (CNBLUE) 소현 2025-05-17 2025-05-17 2025-05-17 아스트로(ASTRO) 민석 2025-05-12 2025-05-12 2025-05-12 아이브 (IVE) 소현 2025-05-17 2025-05-19 2025-05-17 ~ 2025-05-19 아이오아이 (I.O.I) 민석 2025-05-12 2025-05-12 2025-05-12 아이즈원 (IZ*ONE) 소현 2025-05-19 2025-05-19 2025-05-19 업텐션 (UP10TION) 민석 2025-05-12 2025-05-12 2025-05-12 에스에프나인 (SF9) 소현 2025-05-19 2025-05-19 2025-05-19 에스파 (aespa) 민석 2025-05-12 2025-05-14 2025-05-12 ~ 2025-05-14 에이비식스(AB6IX) 소현 2025-05-19 2025-05-19 2025-05-19 에이오에이 (AOA) 민석 2025-05-14 2025-05-14 2025-05-14 에이핑크 (Apink) 소현 2025-05-19 2025-05-19 2025-05-19 엑소 (EXO) 민석 2025-05-14 2025-05-15 2025-05-14 ~ 2025-05-15 엑스원 (X1) 소현 2025-05-19 2025-05-19 2025-05-19 엔믹스 (NMIXX) 민석 2025-05-15 2025-05-16 2025-05-15 ~ 2025-05-16 엔시티 (NCT) 소현 2025-05-19 2025-05-22 2025-05-19 ~ 2025-05-22 여자친구 (GFRIEND) 민석 2025-05-16 2025-05-16 2025-05-16 오마이걸 (OH MY GIRL) 소현 2025-05-22 2025-05-22 2025-05-22 우주소녀 민석 2025-05-16 2025-05-16 2025-05-16 워너원 (Wanna One) 소현 2025-05-22 2025-05-22 2025-05-22 원어스(ONEUS) 민석 2025-05-16 2025-05-16 2025-05-16 원호 (WONHO) 소현 2025-05-22 2025-05-22 2025-05-22 웬디 (WENDY) 민석 2025-05-16 2025-05-16 2025-05-16 위너(WINNER) 소현 2025-05-22 2025-05-23 2025-05-22 ~ 2025-05-23 이달의 소녀 민석 2025-05-16 2025-05-16 2025-05-16 이븐(EVNNE) 소현 2025-05-23 2025-05-23 2025-05-23 인피니트 (Infinite) 민석 2025-05-16 2025-05-16 2025-05-16 있지 (ITZY) 소현 2025-05-23 2025-05-24 2025-05-23 ~ 2025-05-24 제로베이스원 (ZEROBASEONE) 민석 2025-05-16 2025-05-17 2025-05-16 ~ 2025-05-17 종현 (JONGHYUN) 소현 2025-05-24 2025-05-24 2025-05-24 지효 민석 2025-05-17 2025-05-17 2025-05-17 카라 (KARA) 소현 2025-05-24 2025-05-24 2025-05-24 케플러(Kep1er) 민석 2025-05-17 2025-05-17 2025-05-17 태용 (TAEYONG) 소현 2025-05-24 2025-05-24 2025-05-24 투피엠 (2PM) 민석 2025-05-17 2025-05-17 2025-05-17 트레저 (TREASURE) 소현 2025-05-24 2025-05-25 2025-05-24 ~ 2025-05-25 트와이스(TWICE) 민석 2025-05-17 2025-05-18 2025-05-17 ~ 2025-05-18 티아라 (T-ara) 소현 2025-05-25 2025-05-25 2025-05-25 펜타곤 (PENTAGON) 민석 2025-05-18 2025-05-18 2025-05-18 프로미스나인 (fromis_9) 소현 2025-05-25 2025-05-27 2025-05-25 ~ 2025-05-27 02:00:00 아아린 2025-05-04 2025-05-04 2025-05-04 DKZ 재훈 2025-05-04 2025-05-04 2025-05-04 EXID 비진 2025-05-04 2025-05-04 2025-05-04 EXO-K 윤서 2025-05-04 2025-05-04 2025-05-04 EXO-M 병한 2025-05-04 2025-05-04 2025-05-04 FT아일랜드 (FTISLAND) 아아린 2025-05-04 2025-05-04 2025-05-04 GD X TAEYANG 재훈 2025-05-04 2025-05-04 2025-05-04 GD, TOP 비진 2025-05-04 2025-05-04 2025-05-04 JBJ95 윤서 2025-05-04 2025-05-04 2025-05-04 JJ Project 병한 2025-05-04 2025-05-04 2025-05-04 JYJ 아아린 2025-05-04 2025-05-04 2025-05-04 MOBB (MINO,BOBBY) 재훈 2025-05-04 2025-05-04 2025-05-04 MXM (BRANDNEW BOYS) 비진 2025-05-04 2025-05-04 2025-05-04 NCT 127 윤서 2025-05-04 2025-05-07 2025-05-04 ~ 2025-05-07 NCT 도재정 병한 2025-05-04 2025-05-04 2025-05-04 SS501 아아린 2025-05-04 2025-05-04 2025-05-04 god 재훈 2025-05-04 2025-05-04 2025-05-04 강다니엘 비진 2025-05-04 2025-05-04 2025-05-04 강승윤 윤서 2025-05-07 2025-05-07 2025-05-07 걸스데이 (Girl's Day) 병한 2025-05-04 2025-05-04 2025-05-04 구구단 (gugudan) 아아린 2025-05-04 2025-05-04 2025-05-04 권지용(G-Dragon) 재훈 2025-05-04 2025-05-06 2025-05-04 ~ 2025-05-06 규현 (KYUHYUN) 비진 2025-05-04 2025-05-04 2025-05-04 기현 윤서 2025-05-07 2025-05-07 2025-05-07 김성규 병한 2025-05-04 2025-05-04 2025-05-04 김우석 아아린 2025-05-04 2025-05-04 2025-05-04 김재중 (JYJ) 재훈 2025-05-06 2025-05-06 2025-05-06 김재환 비진 2025-05-04 2025-05-04 2025-05-04 김진우 (JINU) 윤서 2025-05-07 2025-05-07 2025-05-07 김현중 병한 2025-05-04 2025-05-04 2025-05-04 남우현 아아린 2025-05-04 2025-05-04 2025-05-04 뉴이스트 (NU`EST) 재훈 2025-05-06 2025-05-06 2025-05-06 뉴이스트 W 비진 2025-05-04 2025-05-04 2025-05-04 니엘 (NIEL) 윤서 2025-05-07 2025-05-07 2025-05-07 다비치 병한 2025-05-04 2025-05-04 2025-05-04 동방신기 (TVXQ!) 아아린 2025-05-04 2025-05-04 2025-05-04 디오 (D.O.) 재훈 2025-05-06 2025-05-06 2025-05-06 레드벨벳(Red Velvet) 비진 2025-05-04 2025-05-06 2025-05-04 ~ 2025-05-06 레드벨벳-아이린&amp;슬기 윤서 2025-05-07 2025-05-07 2025-05-07 레인보우 (Rainbow) 병한 2025-05-04 2025-05-04 2025-05-04 려욱 (RYEOWOOK) 아아린 2025-05-04 2025-05-04 2025-05-04 로이킴 재훈 2025-05-06 2025-05-06 2025-05-06 문빈 비진 2025-05-06 2025-05-06 2025-05-06 미쓰에이(miss A) 윤서 2025-05-07 2025-05-07 2025-05-07 민윤기 (SUGA) 병한 2025-05-04 2025-05-06 2025-05-04 ~ 2025-05-06 박유천 아아린 2025-05-04 2025-05-04 2025-05-04 박재범 재훈 2025-05-06 2025-05-06 2025-05-06 박지훈 비진 2025-05-06 2025-05-06 2025-05-06 배진영 윤서 2025-05-07 2025-05-07 2025-05-07 백현 (BAEKHYUN) 병한 2025-05-06 2025-05-08 2025-05-06 ~ 2025-05-08 뱀뱀 (BamBam) 아아린 2025-05-04 2025-05-04 2025-05-04 보아 (BoA) 재훈 2025-05-06 2025-05-06 2025-05-06 부석순 (SEVENTEEN) 비진 2025-05-06 2025-05-06 2025-05-06 뷔 (V) 윤서 2025-05-07 2025-05-10 2025-05-07 ~ 2025-05-10 브라운 아이드 소울 (Brown Eyed Soul) 병한 2025-05-08 2025-05-08 2025-05-08 브라운아이드걸스 아아린 2025-05-04 2025-05-04 2025-05-04 블랙핑크 (BLACKPINK) 재훈 2025-05-06 2025-05-09 2025-05-06 ~ 2025-05-09 비스트 (Beast) 비진 2025-05-06 2025-05-06 2025-05-06 빅스 (VIXX) 윤서 2025-05-10 2025-05-10 2025-05-10 빅스LR 병한 2025-05-08 2025-05-08 2025-05-08 사무엘 (Samuel) 아아린 2025-05-04 2025-05-04 2025-05-04 서태지 재훈 2025-05-09 2025-05-09 2025-05-09 서현 (SEOHYUN) 비진 2025-05-06 2025-05-06 2025-05-06 세븐 (SE7EN) 윤서 2025-05-10 2025-05-10 2025-05-10 세훈 (SEHUN) 병한 2025-05-08 2025-05-08 2025-05-08 소녀시대 (GIRLS' GENERATION) 아아린 2025-05-04 2025-05-06 2025-05-04 ~ 2025-05-06 소녀시대-태티서 (Girls` Generation-TTS) 재훈 2025-05-09 2025-05-09 2025-05-09 송민호 (MINO) 비진 2025-05-06 2025-05-06 2025-05-06 수지(Suzy) 윤서 2025-05-10 2025-05-10 2025-05-10 수호 (SUHO) 병한 2025-05-08 2025-05-08 2025-05-08 스트레이 키즈 (Stray Kids) 아아린 2025-05-06 2025-05-08 2025-05-06 ~ 2025-05-08 승리 재훈 2025-05-09 2025-05-09 2025-05-09 시우민 (XIUMIN) 비진 2025-05-06 2025-05-06 2025-05-06 시크릿 (Secret) 윤서 2025-05-10 2025-05-10 2025-05-10 신혜성 병한 2025-05-08 2025-05-08 2025-05-08 신화 아아린 2025-05-08 2025-05-08 2025-05-08 싸이 (PSY) 재훈 2025-05-09 2025-05-09 2025-05-09 싸이커스(xikers) 비진 2025-05-06 2025-05-06 2025-05-06 씨스타 (Sistar) 윤서 2025-05-10 2025-05-10 2025-05-10 아이유 (IU) 병한 2025-05-08 2025-05-12 2025-05-08 ~ 2025-05-12 아이콘 (iKON) 아아린 2025-05-08 2025-05-08 2025-05-08 악뮤 (AKMU) 재훈 2025-05-09 2025-05-09 2025-05-09 알엠 (RM) 비진 2025-05-06 2025-05-06 2025-05-06 애프터스쿨 (After School) 윤서 2025-05-10 2025-05-10 2025-05-10 양요섭 병한 2025-05-12 2025-05-12 2025-05-12 에이티즈 (ATEEZ) 아아린 2025-05-08 2025-05-10 2025-05-08 ~ 2025-05-10 엔시티 드림(NCT DREAM) 재훈 2025-05-09 2025-05-12 2025-05-09 ~ 2025-05-12 엔싸인 (n.SSign) 비진 2025-05-06 2025-05-06 2025-05-06 엔플라잉 (N.Flying) 윤서 2025-05-10 2025-05-10 2025-05-10 엔하이픈(ENHYPEN) 병한 2025-05-12 2025-05-16 2025-05-12 ~ 2025-05-16 엠버 (AMBER) 아아린 2025-05-10 2025-05-10 2025-05-10 엠블랙 (MBLAQ) 재훈 2025-05-12 2025-05-12 2025-05-12 예성 (YESUNG) 비진 2025-05-06 2025-05-06 2025-05-06 온앤오프 (ONF) 윤서 2025-05-10 2025-05-10 2025-05-10 온유 (ONEW) 병한 2025-05-16 2025-05-16 2025-05-16 용국&amp;시현 아아린 2025-05-10 2025-05-10 2025-05-10 용준형 재훈 2025-05-12 2025-05-12 2025-05-12 원더걸스 (Wonder Girls) 비진 2025-05-06 2025-05-06 2025-05-06 위아이 (WEi) 윤서 2025-05-10 2025-05-10 2025-05-10 위키미키 (Weki Meki) 병한 2025-05-16 2025-05-16 2025-05-16 유노윤호 (U-KNOW) 아아린 2025-05-10 2025-05-10 2025-05-10 유앤비 (UNB) 재훈 2025-05-12 2025-05-12 2025-05-12 유키스 (U-Kiss) 비진 2025-05-06 2025-05-06 2025-05-06 윤아 (YOONA) 윤서 2025-05-10 2025-05-10 2025-05-10 윤하 병한 2025-05-16 2025-05-16 2025-05-16 은지원 아아린 2025-05-10 2025-05-10 2025-05-10 이진혁 재훈 2025-05-12 2025-05-12 2025-05-12 이하이 비진 2025-05-06 2025-05-06 2025-05-06 이홍기 윤서 2025-05-10 2025-05-10 2025-05-10 이효리 병한 2025-05-16 2025-05-16 2025-05-16 장우영 아아린 2025-05-10 2025-05-10 2025-05-10 장현승 재훈 2025-05-12 2025-05-12 2025-05-12 저스투 (Jus2) 비진 2025-05-06 2025-05-06 2025-05-06 전진 윤서 2025-05-10 2025-05-10 2025-05-10 전효성 병한 2025-05-16 2025-05-16 2025-05-16 정국 아아린 2025-05-10 2025-05-11 2025-05-10 ~ 2025-05-11 정세운 재훈 2025-05-12 2025-05-12 2025-05-12 정용화 (Jung Yong Hwa) 비진 2025-05-06 2025-05-06 2025-05-06 정은지 윤서 2025-05-10 2025-05-10 2025-05-10 제국의아이들 (ZE:A) 병한 2025-05-16 2025-05-16 2025-05-16 제니 (JENNIE) 아아린 2025-05-11 2025-05-12 2025-05-11 ~ 2025-05-12 제시카 (Jessica) 재훈 2025-05-12 2025-05-12 2025-05-12 제이홉(j-hope) 비진 2025-05-06 2025-05-06 2025-05-06 젝스키스 윤서 2025-05-10 2025-05-10 2025-05-10 조승연(WOODZ) 병한 2025-05-16 2025-05-16 2025-05-16 준케이 (JUN. K) 아아린 2025-05-12 2025-05-12 2025-05-12 지민 재훈 2025-05-12 2025-05-15 2025-05-12 ~ 2025-05-15 지수 (JISOO) 비진 2025-05-06 2025-05-06 2025-05-06 지코 (ZICO) 윤서 2025-05-10 2025-05-12 2025-05-10 ~ 2025-05-12 진 (JIN) 병한 2025-05-16 2025-05-18 2025-05-16 ~ 2025-05-18 첸 (CHEN) 아아린 2025-05-12 2025-05-12 2025-05-12 첸백시 (EXO-CBX) 재훈 2025-05-15 2025-05-15 2025-05-15 초신성 비진 2025-05-06 2025-05-06 2025-05-06 최강창민 (MAX CHANGMIN) 윤서 2025-05-12 2025-05-12 2025-05-12 카이 (KAI) 병한 2025-05-18 2025-05-18 2025-05-18 크레비티 (CRAVITY) 아아린 2025-05-12 2025-05-12 2025-05-12 키 (KEY) 재훈 2025-05-15 2025-05-15 2025-05-15 탑 (T.O.P) 비진 2025-05-06 2025-05-06 2025-05-06 태민 (TAEMIN) 윤서 2025-05-12 2025-05-14 2025-05-12 ~ 2025-05-14 태양 병한 2025-05-18 2025-05-18 2025-05-18 태연 (TAEYEON) 아아린 2025-05-12 2025-05-13 2025-05-12 ~ 2025-05-13 투모로우바이투게더 재훈 2025-05-15 2025-05-18 2025-05-15 ~ 2025-05-18 투하트(우현,키) 비진 2025-05-06 2025-05-06 2025-05-06 티파니 (TIFFANY) 윤서 2025-05-14 2025-05-14 2025-05-14 틴탑 (Teen Top) 병한 2025-05-18 2025-05-18 2025-05-18 포미닛(4Minute) 아아린 2025-05-13 2025-05-13 2025-05-13 프리스틴 (PRISTIN) 재훈 2025-05-18 2025-05-18 2025-05-18 플라이 투 더 스카이 (Fly To The Sky) 비진 2025-05-06 2025-05-09 2025-05-06 ~ 2025-05-09 플레이브 (PLAVE) 윤서 2025-05-14 2025-05-17 2025-05-14 ~ 2025-05-17 피원하모니(P1Harmony) 병한 2025-05-18 2025-05-22 2025-05-18 ~ 2025-05-22 하성운 아아린 2025-05-13 2025-05-13 2025-05-13 하이라이트(Highlight) 재훈 2025-05-18 2025-05-18 2025-05-18 한승우 비진 2025-05-09 2025-05-09 2025-05-09 허영생 윤서 2025-05-17 2025-05-19 2025-05-17 ~ 2025-05-19 헨리 (Henry) 병한 2025-05-22 2025-05-22 2025-05-22 히스토리 (HISTORY) 아아린 2025-05-13 2025-05-13 2025-05-13</t>
   </si>
   <si>
     <t>2025-05-04 ~ 2025-05-06</t>
@@ -2295,7 +2247,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2371,12 +2323,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -2390,21 +2336,15 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2427,42 +2367,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2499,25 +2409,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2530,7 +2421,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2858,7 +2749,7 @@
     <col min="6" max="6" width="65.5" customWidth="1"/>
     <col min="7" max="7" width="26.796875" style="3" customWidth="1"/>
     <col min="8" max="8" width="32.3984375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="23.796875" style="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.796875" style="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
@@ -2915,8 +2806,8 @@
       <c r="H2" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I2" s="27" t="s">
-        <v>703</v>
+      <c r="I2" s="20" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -2944,7 +2835,7 @@
       <c r="H3" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -2973,7 +2864,7 @@
       <c r="H4" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I4" s="23">
+      <c r="I4" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -3002,7 +2893,7 @@
       <c r="H5" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -3031,7 +2922,7 @@
       <c r="H6" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -3060,7 +2951,7 @@
       <c r="H7" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -3089,7 +2980,7 @@
       <c r="H8" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -3118,7 +3009,7 @@
       <c r="H9" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -3147,7 +3038,7 @@
       <c r="H10" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -3176,7 +3067,7 @@
       <c r="H11" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -3205,7 +3096,7 @@
       <c r="H12" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="16">
         <v>45785</v>
       </c>
     </row>
@@ -3234,7 +3125,7 @@
       <c r="H13" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="16">
         <v>45782</v>
       </c>
     </row>
@@ -3263,7 +3154,7 @@
       <c r="H14" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -3292,7 +3183,7 @@
       <c r="H15" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="16">
         <v>45782</v>
       </c>
     </row>
@@ -3321,7 +3212,7 @@
       <c r="H16" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -3350,7 +3241,7 @@
       <c r="H17" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="16">
         <v>45782</v>
       </c>
     </row>
@@ -3379,7 +3270,7 @@
       <c r="H18" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="16">
         <v>45790</v>
       </c>
     </row>
@@ -3408,7 +3299,7 @@
       <c r="H19" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="16">
         <v>45784</v>
       </c>
     </row>
@@ -3437,7 +3328,7 @@
       <c r="H20" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="16">
         <v>45790</v>
       </c>
     </row>
@@ -3466,7 +3357,7 @@
       <c r="H21" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="16">
         <v>45784</v>
       </c>
     </row>
@@ -3495,7 +3386,7 @@
       <c r="H22" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="16">
         <v>45791</v>
       </c>
     </row>
@@ -3524,7 +3415,7 @@
       <c r="H23" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I23" s="23">
+      <c r="I23" s="16">
         <v>45786</v>
       </c>
     </row>
@@ -3553,7 +3444,7 @@
       <c r="H24" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I24" s="23">
+      <c r="I24" s="16">
         <v>45792</v>
       </c>
     </row>
@@ -3582,7 +3473,7 @@
       <c r="H25" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I25" s="23">
+      <c r="I25" s="16">
         <v>45786</v>
       </c>
     </row>
@@ -3611,7 +3502,7 @@
       <c r="H26" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I26" s="23">
+      <c r="I26" s="16">
         <v>45792</v>
       </c>
     </row>
@@ -3640,7 +3531,7 @@
       <c r="H27" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I27" s="23">
+      <c r="I27" s="16">
         <v>45786</v>
       </c>
     </row>
@@ -3669,7 +3560,7 @@
       <c r="H28" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I28" s="23">
+      <c r="I28" s="16">
         <v>45793</v>
       </c>
     </row>
@@ -3698,7 +3589,7 @@
       <c r="H29" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I29" s="23">
+      <c r="I29" s="16">
         <v>45786</v>
       </c>
     </row>
@@ -3727,7 +3618,7 @@
       <c r="H30" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I30" s="23">
+      <c r="I30" s="16">
         <v>45794</v>
       </c>
     </row>
@@ -3756,7 +3647,7 @@
       <c r="H31" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I31" s="23">
+      <c r="I31" s="16">
         <v>45788</v>
       </c>
     </row>
@@ -3785,7 +3676,7 @@
       <c r="H32" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I32" s="23">
+      <c r="I32" s="16">
         <v>45794</v>
       </c>
     </row>
@@ -3814,7 +3705,7 @@
       <c r="H33" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I33" s="23">
+      <c r="I33" s="16">
         <v>45788</v>
       </c>
     </row>
@@ -3843,7 +3734,7 @@
       <c r="H34" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I34" s="23">
+      <c r="I34" s="16">
         <v>45794</v>
       </c>
     </row>
@@ -3872,7 +3763,7 @@
       <c r="H35" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I35" s="23">
+      <c r="I35" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -3901,7 +3792,7 @@
       <c r="H36" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I36" s="23">
+      <c r="I36" s="16">
         <v>45794</v>
       </c>
     </row>
@@ -3930,7 +3821,7 @@
       <c r="H37" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I37" s="23">
+      <c r="I37" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -3959,7 +3850,7 @@
       <c r="H38" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I38" s="23">
+      <c r="I38" s="16">
         <v>45794</v>
       </c>
     </row>
@@ -3988,7 +3879,7 @@
       <c r="H39" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I39" s="23">
+      <c r="I39" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -4017,7 +3908,7 @@
       <c r="H40" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I40" s="23">
+      <c r="I40" s="16">
         <v>45796</v>
       </c>
     </row>
@@ -4046,7 +3937,7 @@
       <c r="H41" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I41" s="23">
+      <c r="I41" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -4075,7 +3966,7 @@
       <c r="H42" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I42" s="23">
+      <c r="I42" s="16">
         <v>45796</v>
       </c>
     </row>
@@ -4104,7 +3995,7 @@
       <c r="H43" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I43" s="23">
+      <c r="I43" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -4133,7 +4024,7 @@
       <c r="H44" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I44" s="23">
+      <c r="I44" s="16">
         <v>45796</v>
       </c>
     </row>
@@ -4162,7 +4053,7 @@
       <c r="H45" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I45" s="23">
+      <c r="I45" s="16">
         <v>45791</v>
       </c>
     </row>
@@ -4191,7 +4082,7 @@
       <c r="H46" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I46" s="23">
+      <c r="I46" s="16">
         <v>45796</v>
       </c>
     </row>
@@ -4220,7 +4111,7 @@
       <c r="H47" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I47" s="23">
+      <c r="I47" s="16">
         <v>45791</v>
       </c>
     </row>
@@ -4249,7 +4140,7 @@
       <c r="H48" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I48" s="23">
+      <c r="I48" s="16">
         <v>45796</v>
       </c>
     </row>
@@ -4278,7 +4169,7 @@
       <c r="H49" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I49" s="23">
+      <c r="I49" s="16">
         <v>45792</v>
       </c>
     </row>
@@ -4307,7 +4198,7 @@
       <c r="H50" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I50" s="23">
+      <c r="I50" s="16">
         <v>45796</v>
       </c>
     </row>
@@ -4336,8 +4227,8 @@
       <c r="H51" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I51" s="23" t="s">
-        <v>704</v>
+      <c r="I51" s="16" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
@@ -4365,7 +4256,7 @@
       <c r="H52" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I52" s="23">
+      <c r="I52" s="16">
         <v>45799</v>
       </c>
     </row>
@@ -4394,7 +4285,7 @@
       <c r="H53" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I53" s="23">
+      <c r="I53" s="16">
         <v>45793</v>
       </c>
     </row>
@@ -4423,7 +4314,7 @@
       <c r="H54" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I54" s="23">
+      <c r="I54" s="16">
         <v>45799</v>
       </c>
     </row>
@@ -4452,7 +4343,7 @@
       <c r="H55" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I55" s="23">
+      <c r="I55" s="16">
         <v>45793</v>
       </c>
     </row>
@@ -4481,7 +4372,7 @@
       <c r="H56" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I56" s="23">
+      <c r="I56" s="16">
         <v>45799</v>
       </c>
     </row>
@@ -4510,7 +4401,7 @@
       <c r="H57" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I57" s="23">
+      <c r="I57" s="16">
         <v>45793</v>
       </c>
     </row>
@@ -4539,7 +4430,7 @@
       <c r="H58" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I58" s="23">
+      <c r="I58" s="16">
         <v>45799</v>
       </c>
     </row>
@@ -4568,8 +4459,8 @@
       <c r="H59" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I59" s="23" t="s">
-        <v>706</v>
+      <c r="I59" s="16" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.4">
@@ -4597,7 +4488,7 @@
       <c r="H60" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I60" s="23">
+      <c r="I60" s="16">
         <v>45800</v>
       </c>
     </row>
@@ -4626,7 +4517,7 @@
       <c r="H61" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I61" s="23">
+      <c r="I61" s="16">
         <v>45793</v>
       </c>
     </row>
@@ -4655,7 +4546,7 @@
       <c r="H62" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I62" s="23">
+      <c r="I62" s="16">
         <v>45800</v>
       </c>
     </row>
@@ -4684,7 +4575,7 @@
       <c r="H63" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I63" s="23">
+      <c r="I63" s="16">
         <v>45793</v>
       </c>
     </row>
@@ -4713,7 +4604,7 @@
       <c r="H64" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I64" s="23">
+      <c r="I64" s="16">
         <v>45801</v>
       </c>
     </row>
@@ -4742,7 +4633,7 @@
       <c r="H65" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I65" s="23">
+      <c r="I65" s="16">
         <v>45794</v>
       </c>
     </row>
@@ -4771,7 +4662,7 @@
       <c r="H66" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I66" s="23">
+      <c r="I66" s="16">
         <v>45801</v>
       </c>
     </row>
@@ -4800,8 +4691,8 @@
       <c r="H67" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I67" s="23" t="s">
-        <v>705</v>
+      <c r="I67" s="16" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.4">
@@ -4829,7 +4720,7 @@
       <c r="H68" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I68" s="23">
+      <c r="I68" s="16">
         <v>45801</v>
       </c>
     </row>
@@ -4858,7 +4749,7 @@
       <c r="H69" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I69" s="23">
+      <c r="I69" s="16">
         <v>45794</v>
       </c>
     </row>
@@ -4887,7 +4778,7 @@
       <c r="H70" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I70" s="23">
+      <c r="I70" s="16">
         <v>45801</v>
       </c>
     </row>
@@ -4916,7 +4807,7 @@
       <c r="H71" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I71" s="23">
+      <c r="I71" s="16">
         <v>45795</v>
       </c>
     </row>
@@ -4945,7 +4836,7 @@
       <c r="H72" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I72" s="23">
+      <c r="I72" s="16">
         <v>45802</v>
       </c>
     </row>
@@ -4974,7 +4865,7 @@
       <c r="H73" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I73" s="23">
+      <c r="I73" s="16">
         <v>45796</v>
       </c>
     </row>
@@ -5003,7 +4894,7 @@
       <c r="H74" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I74" s="23">
+      <c r="I74" s="16">
         <v>45802</v>
       </c>
     </row>
@@ -5032,7 +4923,7 @@
       <c r="H75" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I75" s="23">
+      <c r="I75" s="16">
         <v>45794</v>
       </c>
     </row>
@@ -5061,7 +4952,7 @@
       <c r="H76" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I76" s="23">
+      <c r="I76" s="16">
         <v>45801</v>
       </c>
     </row>
@@ -5090,7 +4981,7 @@
       <c r="H77" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I77" s="23">
+      <c r="I77" s="16">
         <v>45794</v>
       </c>
     </row>
@@ -5111,7 +5002,7 @@
         <v>680</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>482</v>
@@ -5119,8 +5010,8 @@
       <c r="H78" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I78" s="23" t="s">
-        <v>714</v>
+      <c r="I78" s="16" t="s">
+        <v>702</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.4">
@@ -5140,7 +5031,7 @@
         <v>679</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="G79" s="10" t="s">
         <v>483</v>
@@ -5148,7 +5039,7 @@
       <c r="H79" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I79" s="23">
+      <c r="I79" s="16">
         <v>45795</v>
       </c>
     </row>
@@ -5177,7 +5068,7 @@
       <c r="H80" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I80" s="23">
+      <c r="I80" s="16">
         <v>45802</v>
       </c>
     </row>
@@ -5206,7 +5097,7 @@
       <c r="H81" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I81" s="23">
+      <c r="I81" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -5235,7 +5126,7 @@
       <c r="H82" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I82" s="23">
+      <c r="I82" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -5264,7 +5155,7 @@
       <c r="H83" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I83" s="23">
+      <c r="I83" s="16">
         <v>45794</v>
       </c>
     </row>
@@ -5293,7 +5184,7 @@
       <c r="H84" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I84" s="23">
+      <c r="I84" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -5322,7 +5213,7 @@
       <c r="H85" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I85" s="23">
+      <c r="I85" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -5351,8 +5242,8 @@
       <c r="H86" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I86" s="23" t="s">
-        <v>716</v>
+      <c r="I86" s="16" t="s">
+        <v>704</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.4">
@@ -5380,7 +5271,7 @@
       <c r="H87" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I87" s="23">
+      <c r="I87" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -5409,7 +5300,7 @@
       <c r="H88" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I88" s="23">
+      <c r="I88" s="16">
         <v>45785</v>
       </c>
     </row>
@@ -5438,7 +5329,7 @@
       <c r="H89" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I89" s="23">
+      <c r="I89" s="16">
         <v>45785</v>
       </c>
     </row>
@@ -5467,7 +5358,7 @@
       <c r="H90" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I90" s="23">
+      <c r="I90" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -5496,7 +5387,7 @@
       <c r="H91" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I91" s="23">
+      <c r="I91" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -5525,8 +5416,8 @@
       <c r="H92" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I92" s="23" t="s">
-        <v>715</v>
+      <c r="I92" s="16" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.4">
@@ -5554,7 +5445,7 @@
       <c r="H93" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I93" s="23">
+      <c r="I93" s="16">
         <v>45784</v>
       </c>
     </row>
@@ -5583,7 +5474,7 @@
       <c r="H94" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I94" s="23">
+      <c r="I94" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -5612,7 +5503,7 @@
       <c r="H95" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I95" s="23">
+      <c r="I95" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -5641,7 +5532,7 @@
       <c r="H96" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I96" s="23">
+      <c r="I96" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -5670,7 +5561,7 @@
       <c r="H97" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I97" s="23">
+      <c r="I97" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -5699,7 +5590,7 @@
       <c r="H98" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I98" s="23">
+      <c r="I98" s="16">
         <v>45784</v>
       </c>
     </row>
@@ -5728,8 +5619,8 @@
       <c r="H99" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I99" s="23" t="s">
-        <v>717</v>
+      <c r="I99" s="16" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.4">
@@ -5757,8 +5648,8 @@
       <c r="H100" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I100" s="23" t="s">
-        <v>718</v>
+      <c r="I100" s="16" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.4">
@@ -5786,7 +5677,7 @@
       <c r="H101" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="I101" s="23">
+      <c r="I101" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -5815,7 +5706,7 @@
       <c r="H102" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I102" s="23">
+      <c r="I102" s="16">
         <v>45785</v>
       </c>
     </row>
@@ -5844,7 +5735,7 @@
       <c r="H103" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I103" s="23">
+      <c r="I103" s="16">
         <v>45784</v>
       </c>
     </row>
@@ -5873,7 +5764,7 @@
       <c r="H104" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I104" s="23">
+      <c r="I104" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -5902,7 +5793,7 @@
       <c r="H105" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I105" s="23">
+      <c r="I105" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -5931,7 +5822,7 @@
       <c r="H106" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I106" s="23">
+      <c r="I106" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -5960,7 +5851,7 @@
       <c r="H107" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I107" s="23">
+      <c r="I107" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -5972,7 +5863,7 @@
         <v>108</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="D108" s="8" t="s">
         <v>678</v>
@@ -5989,7 +5880,7 @@
       <c r="H108" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I108" s="23">
+      <c r="I108" s="16">
         <v>45784</v>
       </c>
     </row>
@@ -6018,7 +5909,7 @@
       <c r="H109" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I109" s="23">
+      <c r="I109" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -6039,7 +5930,7 @@
         <v>680</v>
       </c>
       <c r="F110" s="12" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="G110" s="10" t="s">
         <v>522</v>
@@ -6047,7 +5938,7 @@
       <c r="H110" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I110" s="23">
+      <c r="I110" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -6076,7 +5967,7 @@
       <c r="H111" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I111" s="23">
+      <c r="I111" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -6105,7 +5996,7 @@
       <c r="H112" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I112" s="23">
+      <c r="I112" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -6134,7 +6025,7 @@
       <c r="H113" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I113" s="23">
+      <c r="I113" s="16">
         <v>45784</v>
       </c>
     </row>
@@ -6155,7 +6046,7 @@
         <v>680</v>
       </c>
       <c r="F114" s="12" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="G114" s="10" t="s">
         <v>302</v>
@@ -6163,8 +6054,8 @@
       <c r="H114" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I114" s="23" t="s">
-        <v>724</v>
+      <c r="I114" s="16" t="s">
+        <v>712</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.4">
@@ -6184,7 +6075,7 @@
         <v>680</v>
       </c>
       <c r="F115" s="12" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="G115" s="10" t="s">
         <v>303</v>
@@ -6192,7 +6083,7 @@
       <c r="H115" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I115" s="23">
+      <c r="I115" s="16">
         <v>45790</v>
       </c>
     </row>
@@ -6221,8 +6112,8 @@
       <c r="H116" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I116" s="23" t="s">
-        <v>725</v>
+      <c r="I116" s="16" t="s">
+        <v>713</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.4">
@@ -6242,7 +6133,7 @@
         <v>680</v>
       </c>
       <c r="F117" s="12" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="G117" s="10" t="s">
         <v>304</v>
@@ -6250,8 +6141,8 @@
       <c r="H117" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I117" s="23" t="s">
-        <v>727</v>
+      <c r="I117" s="16" t="s">
+        <v>715</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.4">
@@ -6279,8 +6170,8 @@
       <c r="H118" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I118" s="23" t="s">
-        <v>726</v>
+      <c r="I118" s="16" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.4">
@@ -6308,7 +6199,7 @@
       <c r="H119" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I119" s="23">
+      <c r="I119" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -6337,7 +6228,7 @@
       <c r="H120" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I120" s="23">
+      <c r="I120" s="16">
         <v>45785</v>
       </c>
     </row>
@@ -6366,7 +6257,7 @@
       <c r="H121" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I121" s="23">
+      <c r="I121" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -6395,7 +6286,7 @@
       <c r="H122" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I122" s="23">
+      <c r="I122" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -6424,7 +6315,7 @@
       <c r="H123" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I123" s="23">
+      <c r="I123" s="16">
         <v>45784</v>
       </c>
     </row>
@@ -6453,7 +6344,7 @@
       <c r="H124" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I124" s="23">
+      <c r="I124" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -6482,7 +6373,7 @@
       <c r="H125" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I125" s="23">
+      <c r="I125" s="16">
         <v>45785</v>
       </c>
     </row>
@@ -6511,7 +6402,7 @@
       <c r="H126" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I126" s="23">
+      <c r="I126" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -6540,7 +6431,7 @@
       <c r="H127" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I127" s="23">
+      <c r="I127" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -6569,7 +6460,7 @@
       <c r="H128" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I128" s="23">
+      <c r="I128" s="16">
         <v>45784</v>
       </c>
     </row>
@@ -6598,8 +6489,8 @@
       <c r="H129" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I129" s="23" t="s">
-        <v>708</v>
+      <c r="I129" s="16" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.4">
@@ -6627,8 +6518,8 @@
       <c r="H130" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I130" s="23" t="s">
-        <v>729</v>
+      <c r="I130" s="16" t="s">
+        <v>717</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.4">
@@ -6656,7 +6547,7 @@
       <c r="H131" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I131" s="23">
+      <c r="I131" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -6685,8 +6576,8 @@
       <c r="H132" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I132" s="23" t="s">
-        <v>730</v>
+      <c r="I132" s="16" t="s">
+        <v>718</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.4">
@@ -6714,7 +6605,7 @@
       <c r="H133" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I133" s="23">
+      <c r="I133" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -6743,7 +6634,7 @@
       <c r="H134" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I134" s="23">
+      <c r="I134" s="16">
         <v>45785</v>
       </c>
     </row>
@@ -6772,7 +6663,7 @@
       <c r="H135" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I135" s="23">
+      <c r="I135" s="16">
         <v>45781</v>
       </c>
     </row>
@@ -6801,7 +6692,7 @@
       <c r="H136" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I136" s="23">
+      <c r="I136" s="16">
         <v>45786</v>
       </c>
     </row>
@@ -6830,7 +6721,7 @@
       <c r="H137" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I137" s="23">
+      <c r="I137" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -6859,7 +6750,7 @@
       <c r="H138" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I138" s="23">
+      <c r="I138" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -6888,7 +6779,7 @@
       <c r="H139" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I139" s="23">
+      <c r="I139" s="16">
         <v>45785</v>
       </c>
     </row>
@@ -6917,8 +6808,8 @@
       <c r="H140" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I140" s="24" t="s">
-        <v>707</v>
+      <c r="I140" s="17" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.4">
@@ -6946,7 +6837,7 @@
       <c r="H141" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I141" s="23">
+      <c r="I141" s="16">
         <v>45786</v>
       </c>
     </row>
@@ -6975,7 +6866,7 @@
       <c r="H142" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I142" s="23">
+      <c r="I142" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -7004,7 +6895,7 @@
       <c r="H143" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I143" s="23">
+      <c r="I143" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -7033,7 +6924,7 @@
       <c r="H144" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I144" s="23">
+      <c r="I144" s="16">
         <v>45785</v>
       </c>
     </row>
@@ -7062,7 +6953,7 @@
       <c r="H145" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I145" s="23">
+      <c r="I145" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -7091,7 +6982,7 @@
       <c r="H146" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I146" s="23">
+      <c r="I146" s="16">
         <v>45786</v>
       </c>
     </row>
@@ -7120,7 +7011,7 @@
       <c r="H147" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I147" s="23">
+      <c r="I147" s="16">
         <v>45785</v>
       </c>
     </row>
@@ -7149,8 +7040,8 @@
       <c r="H148" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I148" s="23" t="s">
-        <v>731</v>
+      <c r="I148" s="16" t="s">
+        <v>719</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.4">
@@ -7178,7 +7069,7 @@
       <c r="H149" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I149" s="23">
+      <c r="I149" s="16">
         <v>45785</v>
       </c>
     </row>
@@ -7207,7 +7098,7 @@
       <c r="H150" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I150" s="23">
+      <c r="I150" s="16">
         <v>45785</v>
       </c>
     </row>
@@ -7236,7 +7127,7 @@
       <c r="H151" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I151" s="23">
+      <c r="I151" s="16">
         <v>45786</v>
       </c>
     </row>
@@ -7265,7 +7156,7 @@
       <c r="H152" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I152" s="23">
+      <c r="I152" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -7294,8 +7185,8 @@
       <c r="H153" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I153" s="23" t="s">
-        <v>731</v>
+      <c r="I153" s="16" t="s">
+        <v>719</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.4">
@@ -7323,7 +7214,7 @@
       <c r="H154" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I154" s="23">
+      <c r="I154" s="16">
         <v>45785</v>
       </c>
     </row>
@@ -7352,7 +7243,7 @@
       <c r="H155" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I155" s="23">
+      <c r="I155" s="16">
         <v>45785</v>
       </c>
     </row>
@@ -7381,7 +7272,7 @@
       <c r="H156" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I156" s="23">
+      <c r="I156" s="16">
         <v>45786</v>
       </c>
     </row>
@@ -7410,7 +7301,7 @@
       <c r="H157" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I157" s="23">
+      <c r="I157" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -7439,7 +7330,7 @@
       <c r="H158" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I158" s="23">
+      <c r="I158" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -7468,8 +7359,8 @@
       <c r="H159" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I159" s="23" t="s">
-        <v>709</v>
+      <c r="I159" s="16" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.4">
@@ -7497,8 +7388,8 @@
       <c r="H160" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I160" s="23" t="s">
-        <v>728</v>
+      <c r="I160" s="16" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.4">
@@ -7526,7 +7417,7 @@
       <c r="H161" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I161" s="23">
+      <c r="I161" s="16">
         <v>45786</v>
       </c>
     </row>
@@ -7555,7 +7446,7 @@
       <c r="H162" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I162" s="23">
+      <c r="I162" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -7584,7 +7475,7 @@
       <c r="H163" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="I163" s="23">
+      <c r="I163" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -7613,7 +7504,7 @@
       <c r="H164" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I164" s="23">
+      <c r="I164" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -7642,7 +7533,7 @@
       <c r="H165" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I165" s="23">
+      <c r="I165" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -7671,7 +7562,7 @@
       <c r="H166" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I166" s="23">
+      <c r="I166" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -7700,7 +7591,7 @@
       <c r="H167" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I167" s="23">
+      <c r="I167" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -7729,7 +7620,7 @@
       <c r="H168" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I168" s="23">
+      <c r="I168" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -7758,8 +7649,8 @@
       <c r="H169" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I169" s="23" t="s">
-        <v>732</v>
+      <c r="I169" s="16" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.4">
@@ -7787,7 +7678,7 @@
       <c r="H170" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I170" s="23">
+      <c r="I170" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -7816,7 +7707,7 @@
       <c r="H171" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I171" s="23">
+      <c r="I171" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -7845,7 +7736,7 @@
       <c r="H172" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I172" s="23">
+      <c r="I172" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -7874,7 +7765,7 @@
       <c r="H173" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I173" s="23">
+      <c r="I173" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -7903,7 +7794,7 @@
       <c r="H174" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I174" s="23">
+      <c r="I174" s="16">
         <v>45793</v>
       </c>
     </row>
@@ -7932,7 +7823,7 @@
       <c r="H175" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I175" s="23">
+      <c r="I175" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -7961,7 +7852,7 @@
       <c r="H176" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I176" s="23">
+      <c r="I176" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -7990,7 +7881,7 @@
       <c r="H177" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I177" s="23">
+      <c r="I177" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -8019,7 +7910,7 @@
       <c r="H178" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I178" s="23">
+      <c r="I178" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -8048,7 +7939,7 @@
       <c r="H179" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I179" s="23">
+      <c r="I179" s="16">
         <v>45793</v>
       </c>
     </row>
@@ -8077,7 +7968,7 @@
       <c r="H180" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I180" s="23">
+      <c r="I180" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -8106,7 +7997,7 @@
       <c r="H181" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I181" s="23">
+      <c r="I181" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -8135,7 +8026,7 @@
       <c r="H182" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I182" s="23">
+      <c r="I182" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -8164,7 +8055,7 @@
       <c r="H183" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I183" s="23">
+      <c r="I183" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -8193,7 +8084,7 @@
       <c r="H184" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I184" s="23">
+      <c r="I184" s="16">
         <v>45793</v>
       </c>
     </row>
@@ -8222,7 +8113,7 @@
       <c r="H185" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I185" s="23">
+      <c r="I185" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -8251,7 +8142,7 @@
       <c r="H186" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I186" s="23">
+      <c r="I186" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -8280,7 +8171,7 @@
       <c r="H187" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I187" s="23">
+      <c r="I187" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -8309,7 +8200,7 @@
       <c r="H188" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I188" s="23">
+      <c r="I188" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -8338,7 +8229,7 @@
       <c r="H189" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I189" s="23">
+      <c r="I189" s="16">
         <v>45793</v>
       </c>
     </row>
@@ -8367,7 +8258,7 @@
       <c r="H190" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I190" s="23">
+      <c r="I190" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -8396,7 +8287,7 @@
       <c r="H191" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I191" s="23">
+      <c r="I191" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -8425,7 +8316,7 @@
       <c r="H192" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I192" s="23">
+      <c r="I192" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -8454,7 +8345,7 @@
       <c r="H193" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I193" s="23">
+      <c r="I193" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -8483,7 +8374,7 @@
       <c r="H194" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I194" s="23">
+      <c r="I194" s="16">
         <v>45793</v>
       </c>
     </row>
@@ -8512,7 +8403,7 @@
       <c r="H195" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I195" s="23">
+      <c r="I195" s="16">
         <v>45788</v>
       </c>
     </row>
@@ -8541,8 +8432,8 @@
       <c r="H196" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I196" s="23" t="s">
-        <v>711</v>
+      <c r="I196" s="16" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.4">
@@ -8570,7 +8461,7 @@
       <c r="H197" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I197" s="23">
+      <c r="I197" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -8599,7 +8490,7 @@
       <c r="H198" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I198" s="23">
+      <c r="I198" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -8628,7 +8519,7 @@
       <c r="H199" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I199" s="23">
+      <c r="I199" s="16">
         <v>45793</v>
       </c>
     </row>
@@ -8657,7 +8548,7 @@
       <c r="H200" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I200" s="23">
+      <c r="I200" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -8686,7 +8577,7 @@
       <c r="H201" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I201" s="23">
+      <c r="I201" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -8715,7 +8606,7 @@
       <c r="H202" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I202" s="23">
+      <c r="I202" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -8744,7 +8635,7 @@
       <c r="H203" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I203" s="23">
+      <c r="I203" s="16">
         <v>45787</v>
       </c>
     </row>
@@ -8773,7 +8664,7 @@
       <c r="H204" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I204" s="23">
+      <c r="I204" s="16">
         <v>45793</v>
       </c>
     </row>
@@ -8802,7 +8693,7 @@
       <c r="H205" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I205" s="23">
+      <c r="I205" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -8831,7 +8722,7 @@
       <c r="H206" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I206" s="23">
+      <c r="I206" s="16">
         <v>45792</v>
       </c>
     </row>
@@ -8860,8 +8751,8 @@
       <c r="H207" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I207" s="23" t="s">
-        <v>733</v>
+      <c r="I207" s="16" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.4">
@@ -8889,7 +8780,7 @@
       <c r="H208" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I208" s="23">
+      <c r="I208" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -8918,7 +8809,7 @@
       <c r="H209" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I209" s="23">
+      <c r="I209" s="16">
         <v>45795</v>
       </c>
     </row>
@@ -8947,8 +8838,8 @@
       <c r="H210" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I210" s="23" t="s">
-        <v>711</v>
+      <c r="I210" s="16" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.4">
@@ -8976,7 +8867,7 @@
       <c r="H211" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I211" s="23">
+      <c r="I211" s="16">
         <v>45792</v>
       </c>
     </row>
@@ -9005,7 +8896,7 @@
       <c r="H212" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I212" s="23">
+      <c r="I212" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -9034,7 +8925,7 @@
       <c r="H213" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I213" s="23">
+      <c r="I213" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -9063,7 +8954,7 @@
       <c r="H214" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I214" s="23">
+      <c r="I214" s="16">
         <v>45795</v>
       </c>
     </row>
@@ -9092,7 +8983,7 @@
       <c r="H215" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I215" s="23">
+      <c r="I215" s="16">
         <v>45789</v>
       </c>
     </row>
@@ -9121,8 +9012,8 @@
       <c r="H216" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I216" s="23" t="s">
-        <v>710</v>
+      <c r="I216" s="16" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.4">
@@ -9150,7 +9041,7 @@
       <c r="H217" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I217" s="23">
+      <c r="I217" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -9179,7 +9070,7 @@
       <c r="H218" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I218" s="23">
+      <c r="I218" s="16">
         <v>45791</v>
       </c>
     </row>
@@ -9208,7 +9099,7 @@
       <c r="H219" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I219" s="23">
+      <c r="I219" s="16">
         <v>45795</v>
       </c>
     </row>
@@ -9237,7 +9128,7 @@
       <c r="H220" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I220" s="23">
+      <c r="I220" s="16">
         <v>45790</v>
       </c>
     </row>
@@ -9266,7 +9157,7 @@
       <c r="H221" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I221" s="23">
+      <c r="I221" s="16">
         <v>45795</v>
       </c>
     </row>
@@ -9295,7 +9186,7 @@
       <c r="H222" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I222" s="23">
+      <c r="I222" s="16">
         <v>45783</v>
       </c>
     </row>
@@ -9324,7 +9215,7 @@
       <c r="H223" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I223" s="23">
+      <c r="I223" s="16">
         <v>45791</v>
       </c>
     </row>
@@ -9353,7 +9244,7 @@
       <c r="H224" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I224" s="23">
+      <c r="I224" s="16">
         <v>45796</v>
       </c>
     </row>
@@ -9382,7 +9273,7 @@
       <c r="H225" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I225" s="23">
+      <c r="I225" s="16">
         <v>45790</v>
       </c>
     </row>
@@ -9411,18 +9302,18 @@
       <c r="H226" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="I226" s="23">
+      <c r="I226" s="16">
         <v>45795</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="I227" s="25"/>
+      <c r="I227" s="18"/>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="I229" s="25"/>
+      <c r="I229" s="18"/>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="I230" s="25"/>
+      <c r="I230" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -9656,1847 +9547,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId226"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B229"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
-        <v>702</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="59.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B42" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="B44" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="B54" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A55" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="B58" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="B59" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="B60" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="B61" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="59.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B62" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="B63" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A66" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="B66" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A67" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="B67" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A68" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="B68" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A69" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="B69" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A70" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="B70" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A71" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="B71" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A72" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="B72" s="19" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A73" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="B73" s="19" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A74" s="17">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="B74" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A75" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B75" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A76" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B76" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A77" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B77" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A78" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B78" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A79" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B79" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A80" s="16" t="s">
-        <v>691</v>
-      </c>
-      <c r="B80" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A81" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B81" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A82" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B82" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A83" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B83" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A84" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A85" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B85" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A86" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B86" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A87" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B87" s="20" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A88" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B88" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A89" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B89" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A90" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B90" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A91" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B91" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A92" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B92" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A93" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B93" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A94" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B94" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A95" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B95" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A96" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B96" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A97" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B97" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A98" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B98" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A99" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B99" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A100" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B100" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A101" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B101" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A102" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B102" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A103" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B103" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A104" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B104" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A105" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B105" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A106" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B106" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A107" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B107" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A108" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B108" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A109" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B109" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A110" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B110" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A111" s="16" t="s">
-        <v>692</v>
-      </c>
-      <c r="B111" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A112" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B112" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A113" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B113" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A114" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B114" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A115" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B115" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A116" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B116" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A117" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="B117" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A118" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B118" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A119" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="B119" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A120" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B120" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A121" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B121" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A122" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B122" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A123" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B123" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A124" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="B124" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A125" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B125" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A126" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B126" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A127" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B127" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" ht="59.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A128" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B128" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A129" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="B129" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A130" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B130" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A131" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B131" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A132" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B132" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A133" s="16" t="s">
-        <v>693</v>
-      </c>
-      <c r="B133" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A134" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B134" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A135" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B135" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A136" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B136" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A137" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B137" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A138" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B138" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" ht="59.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A139" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="B139" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" ht="73.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A140" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B140" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A141" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B141" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A142" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B142" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A143" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B143" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A144" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B144" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A145" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="B145" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A146" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B146" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A147" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="B147" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A148" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B148" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A149" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B149" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A150" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B150" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A151" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B151" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A152" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B152" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A153" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B153" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A154" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="B154" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A155" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="B155" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A156" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="B156" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A157" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="B157" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A158" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="B158" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A159" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="B159" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A160" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="B160" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A161" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="B161" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A162" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="B162" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A163" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="B163" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A164" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="B164" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A165" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B165" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A166" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="B166" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A167" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B167" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A168" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="B168" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A169" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="B169" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A170" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="B170" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A171" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B171" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A172" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B172" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A173" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="B173" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A174" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="B174" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A175" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="B175" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A176" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="B176" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A177" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="B177" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A178" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="B178" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A179" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="B179" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A180" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="B180" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A181" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="B181" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A182" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B182" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A183" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="B183" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A184" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="B184" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A185" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="B185" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A186" s="16" t="s">
-        <v>694</v>
-      </c>
-      <c r="B186" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A187" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="B187" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A188" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="B188" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A189" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="B189" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A190" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="B190" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A191" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="B191" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A192" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="B192" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A193" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="B193" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A194" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="B194" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A195" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="B195" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A196" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="B196" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A197" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="B197" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A198" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="B198" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A199" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="B199" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A200" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="B200" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A201" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="B201" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A202" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B202" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A203" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="B203" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A204" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="B204" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A205" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="B205" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A206" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="B206" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" ht="59.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A207" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="B207" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A208" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="B208" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A209" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="B209" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A210" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="B210" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A211" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="B211" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A212" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="B212" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A213" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="B213" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A214" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="B214" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A215" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="B215" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A216" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="B216" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A217" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B217" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A218" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="B218" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A219" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="B219" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A220" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="B220" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" ht="59.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A221" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="B221" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A222" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="B222" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" ht="59.4" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A223" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="B223" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A224" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="B224" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" ht="45" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A225" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="B225" s="19" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A226" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="B226" s="19" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A227" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="B227" s="19" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A228" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="B228" s="19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A229" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="B229" s="19" t="s">
-        <v>697</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>